--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="136">
   <si>
     <t>lang_code</t>
   </si>
@@ -56,322 +56,319 @@
     <t>is_active</t>
   </si>
   <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>Pays</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
     <t>eng</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
-    <t>MyCountry</t>
+    <t>NTH</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>MOR/NTH</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>RSK</t>
+  </si>
+  <si>
+    <t>RabatSaleKenitra</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK</t>
+  </si>
+  <si>
+    <t>Rabat-Salé-Kénitra</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>RBT</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK/RBT</t>
+  </si>
+  <si>
+    <t>KTA</t>
+  </si>
+  <si>
+    <t>Kenitra</t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK/KTA</t>
+  </si>
+  <si>
+    <t>Kénitra</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>Salé </t>
+  </si>
+  <si>
+    <t>MOR/NTH/RSK/SAL</t>
+  </si>
+  <si>
+    <t>Sala</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>Casablanca-Settat</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST</t>
+  </si>
+  <si>
+    <t>BSN</t>
+  </si>
+  <si>
+    <t>Benslimane</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/BSN</t>
+  </si>
+  <si>
+    <t>CSB</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/CSB</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Settat</t>
+  </si>
+  <si>
+    <t>MOR/NTH/CST/STT</t>
+  </si>
+  <si>
+    <t>ORT</t>
+  </si>
+  <si>
+    <t>Oriental</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT</t>
+  </si>
+  <si>
+    <t>NDR</t>
+  </si>
+  <si>
+    <t>Nador</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/NDR</t>
+  </si>
+  <si>
+    <t>BRK</t>
+  </si>
+  <si>
+    <t>Berkane</t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/BRK</t>
+  </si>
+  <si>
+    <t>JRD</t>
+  </si>
+  <si>
+    <t>Jerada </t>
+  </si>
+  <si>
+    <t>MOR/NTH/ORT/JRD</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>MOR/STH</t>
+  </si>
+  <si>
+    <t>Sud</t>
+  </si>
+  <si>
+    <t>MRS</t>
+  </si>
+  <si>
+    <t>Marrakesh-Safi</t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS</t>
+  </si>
+  <si>
+    <t>SAF</t>
+  </si>
+  <si>
+    <t>Safi </t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS/SAF</t>
+  </si>
+  <si>
+    <t>YSF</t>
+  </si>
+  <si>
+    <t>Youssoufia </t>
+  </si>
+  <si>
+    <t>MOR/STH/MRS/YSF</t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>Souss-Massa</t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS</t>
+  </si>
+  <si>
+    <t>Sus-Massa</t>
+  </si>
+  <si>
+    <t>TTA</t>
+  </si>
+  <si>
+    <t>Tata </t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS/TTA</t>
+  </si>
+  <si>
+    <t>TZT</t>
+  </si>
+  <si>
+    <t>Tiznit</t>
+  </si>
+  <si>
+    <t>MOR/STH/SOS/TZT</t>
+  </si>
+  <si>
+    <t>ara</t>
+  </si>
+  <si>
+    <t>مايكونتري</t>
+  </si>
+  <si>
+    <t>دولة</t>
+  </si>
+  <si>
+    <t>شمال</t>
+  </si>
+  <si>
+    <t>اتجاه</t>
+  </si>
+  <si>
+    <t>الرباط ساليالقنيطرة</t>
+  </si>
+  <si>
+    <t>منطقة</t>
+  </si>
+  <si>
+    <t>الرباط</t>
+  </si>
+  <si>
+    <t>مقاطعة</t>
+  </si>
+  <si>
+    <t>القنيطرة</t>
+  </si>
+  <si>
+    <t>قذر</t>
+  </si>
+  <si>
+    <t>الدار البيضاء سطات</t>
+  </si>
+  <si>
+    <t>بن سليمان</t>
+  </si>
+  <si>
+    <t>الدار البيضاء</t>
+  </si>
+  <si>
+    <t>سطات</t>
+  </si>
+  <si>
+    <t>شرقية</t>
+  </si>
+  <si>
+    <t>الناظور</t>
+  </si>
+  <si>
+    <t>بركان</t>
+  </si>
+  <si>
+    <t>جرادة</t>
+  </si>
+  <si>
+    <t>جنوب</t>
+  </si>
+  <si>
+    <t>مراكشصف</t>
+  </si>
+  <si>
+    <t>صافي</t>
+  </si>
+  <si>
+    <t>اليوسفية</t>
+  </si>
+  <si>
+    <t>سوس ماسة</t>
+  </si>
+  <si>
+    <t>تاتا</t>
+  </si>
+  <si>
+    <t>تزنيت</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
   </si>
   <si>
     <t>Country</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>Maroc</t>
-  </si>
-  <si>
-    <t>Pays</t>
-  </si>
-  <si>
-    <t>NTH</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>MOR/NTH</t>
-  </si>
-  <si>
-    <t>Nord</t>
-  </si>
-  <si>
-    <t>RSK</t>
-  </si>
-  <si>
-    <t>RabatSaleKenitra</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>MOR/NTH/RSK</t>
-  </si>
-  <si>
-    <t>Rabat-Salé-Kénitra</t>
-  </si>
-  <si>
-    <t>Région</t>
-  </si>
-  <si>
-    <t>RBT</t>
-  </si>
-  <si>
-    <t>Rabat</t>
-  </si>
-  <si>
-    <t>Province</t>
-  </si>
-  <si>
-    <t>MOR/NTH/RSK/RBT</t>
-  </si>
-  <si>
-    <t>KTA</t>
-  </si>
-  <si>
-    <t>Kenitra</t>
-  </si>
-  <si>
-    <t>MOR/NTH/RSK/KTA</t>
-  </si>
-  <si>
-    <t>Kénitra</t>
-  </si>
-  <si>
-    <t>SAL</t>
-  </si>
-  <si>
-    <t>Salé </t>
-  </si>
-  <si>
-    <t>MOR/NTH/RSK/SAL</t>
-  </si>
-  <si>
-    <t>Sala</t>
-  </si>
-  <si>
-    <t>CST</t>
-  </si>
-  <si>
-    <t>Casablanca-Settat</t>
-  </si>
-  <si>
-    <t>MOR/NTH/CST</t>
-  </si>
-  <si>
-    <t>BSN</t>
-  </si>
-  <si>
-    <t>Benslimane</t>
-  </si>
-  <si>
-    <t>MOR/NTH/CST/BSN</t>
-  </si>
-  <si>
-    <t>CSB</t>
-  </si>
-  <si>
-    <t>Casablanca</t>
-  </si>
-  <si>
-    <t>MOR/NTH/CST/CSB</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Settat</t>
-  </si>
-  <si>
-    <t>MOR/NTH/CST/STT</t>
-  </si>
-  <si>
-    <t>ORT</t>
-  </si>
-  <si>
-    <t>Oriental</t>
-  </si>
-  <si>
-    <t>MOR/NTH/ORT</t>
-  </si>
-  <si>
-    <t>NDR</t>
-  </si>
-  <si>
-    <t>Nador</t>
-  </si>
-  <si>
-    <t>MOR/NTH/ORT/NDR</t>
-  </si>
-  <si>
-    <t>BRK</t>
-  </si>
-  <si>
-    <t>Berkane</t>
-  </si>
-  <si>
-    <t>MOR/NTH/ORT/BRK</t>
-  </si>
-  <si>
-    <t>JRD</t>
-  </si>
-  <si>
-    <t>Jerada </t>
-  </si>
-  <si>
-    <t>MOR/NTH/ORT/JRD</t>
-  </si>
-  <si>
-    <t>STH</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>MOR/STH</t>
-  </si>
-  <si>
-    <t>Sud</t>
-  </si>
-  <si>
-    <t>MRS</t>
-  </si>
-  <si>
-    <t>Marrakesh-Safi</t>
-  </si>
-  <si>
-    <t>MOR/STH/MRS</t>
-  </si>
-  <si>
-    <t>SAF</t>
-  </si>
-  <si>
-    <t>Safi </t>
-  </si>
-  <si>
-    <t>MOR/STH/MRS/SAF</t>
-  </si>
-  <si>
-    <t>YSF</t>
-  </si>
-  <si>
-    <t>Youssoufia </t>
-  </si>
-  <si>
-    <t>MOR/STH/MRS/YSF</t>
-  </si>
-  <si>
-    <t>SOS</t>
-  </si>
-  <si>
-    <t>Souss-Massa</t>
-  </si>
-  <si>
-    <t>MOR/STH/SOS</t>
-  </si>
-  <si>
-    <t>Sus-Massa</t>
-  </si>
-  <si>
-    <t>TTA</t>
-  </si>
-  <si>
-    <t>Tata </t>
-  </si>
-  <si>
-    <t>MOR/STH/SOS/TTA</t>
-  </si>
-  <si>
-    <t>TZT</t>
-  </si>
-  <si>
-    <t>Tiznit</t>
-  </si>
-  <si>
-    <t>MOR/STH/SOS/TZT</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>مايكونتري</t>
-  </si>
-  <si>
-    <t>دولة</t>
-  </si>
-  <si>
-    <t>شمال</t>
-  </si>
-  <si>
-    <t>اتجاه</t>
-  </si>
-  <si>
-    <t>الرباط ساليالقنيطرة</t>
-  </si>
-  <si>
-    <t>منطقة</t>
-  </si>
-  <si>
-    <t>الرباط</t>
-  </si>
-  <si>
-    <t>مقاطعة</t>
-  </si>
-  <si>
-    <t>القنيطرة</t>
-  </si>
-  <si>
-    <t>قذر</t>
-  </si>
-  <si>
-    <t>الدار البيضاء سطات</t>
-  </si>
-  <si>
-    <t>بن سليمان</t>
-  </si>
-  <si>
-    <t>الدار البيضاء</t>
-  </si>
-  <si>
-    <t>سطات</t>
-  </si>
-  <si>
-    <t>شرقية</t>
-  </si>
-  <si>
-    <t>الناظور</t>
-  </si>
-  <si>
-    <t>بركان</t>
-  </si>
-  <si>
-    <t>جرادة</t>
-  </si>
-  <si>
-    <t>جنوب</t>
-  </si>
-  <si>
-    <t>مراكشصف</t>
-  </si>
-  <si>
-    <t>صافي</t>
-  </si>
-  <si>
-    <t>اليوسفية</t>
-  </si>
-  <si>
-    <t>سوس ماسة</t>
-  </si>
-  <si>
-    <t>تاتا</t>
-  </si>
-  <si>
-    <t>تزنيت</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>Lesotho</t>
   </si>
   <si>
     <t>BUE</t>
@@ -812,7 +809,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -856,19 +853,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1009,7 +993,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1021,34 +1005,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,7 +1117,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1153,9 +1137,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1478,7 +1459,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="17.8571428571429" style="1" customWidth="1"/>
@@ -1515,7 +1496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" hidden="1" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1509,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1538,47 +1519,50 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:8">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" hidden="1" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>9</v>
@@ -1587,142 +1571,142 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" hidden="1" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:8">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" hidden="1" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:8">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" hidden="1" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1731,24 +1715,24 @@
         <v>3</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:8">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>34</v>
@@ -1757,24 +1741,24 @@
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" hidden="1" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>36</v>
@@ -1783,466 +1767,466 @@
         <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:8">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" hidden="1" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:8">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" hidden="1" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="1">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:8">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" hidden="1" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:8">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" hidden="1" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="1">
-        <v>3</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:8">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" hidden="1" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:8">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" hidden="1" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:8">
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" hidden="1" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="1">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:8">
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" hidden="1" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:8">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" hidden="1" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>64</v>
@@ -2251,10 +2235,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>9</v>
@@ -2263,194 +2247,194 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:8">
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" hidden="1" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:8">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" hidden="1" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="G34" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:8">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" hidden="1" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="1">
-        <v>3</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:8">
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" hidden="1" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>77</v>
@@ -2459,117 +2443,117 @@
         <v>2</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:8">
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" hidden="1" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="1">
-        <v>3</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:8">
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" hidden="1" spans="1:8">
       <c r="A42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="1">
-        <v>3</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>12</v>
@@ -2577,25 +2561,22 @@
     </row>
     <row r="43" hidden="1" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>12</v>
@@ -2603,21 +2584,24 @@
     </row>
     <row r="44" hidden="1" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>88</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H44" s="3" t="s">
@@ -2626,25 +2610,25 @@
     </row>
     <row r="45" hidden="1" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>12</v>
@@ -2652,25 +2636,25 @@
     </row>
     <row r="46" hidden="1" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="9" t="s">
         <v>92</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>12</v>
@@ -2678,10 +2662,10 @@
     </row>
     <row r="47" hidden="1" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>93</v>
@@ -2689,14 +2673,14 @@
       <c r="D47" s="1">
         <v>3</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>94</v>
+      <c r="E47" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>12</v>
@@ -2704,25 +2688,25 @@
     </row>
     <row r="48" hidden="1" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>94</v>
+      <c r="E48" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>12</v>
@@ -2730,25 +2714,25 @@
     </row>
     <row r="49" hidden="1" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="1">
-        <v>3</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>94</v>
+        <v>2</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>12</v>
@@ -2756,25 +2740,25 @@
     </row>
     <row r="50" hidden="1" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50" s="1">
-        <v>2</v>
-      </c>
-      <c r="E50" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>92</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>12</v>
@@ -2782,25 +2766,25 @@
     </row>
     <row r="51" hidden="1" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>94</v>
+      <c r="E51" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>12</v>
@@ -2808,25 +2792,25 @@
     </row>
     <row r="52" hidden="1" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>94</v>
+      <c r="E52" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>12</v>
@@ -2834,25 +2818,25 @@
     </row>
     <row r="53" hidden="1" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D53" s="1">
-        <v>3</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>94</v>
+        <v>2</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>12</v>
@@ -2860,25 +2844,25 @@
     </row>
     <row r="54" hidden="1" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>92</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>12</v>
@@ -2886,25 +2870,25 @@
     </row>
     <row r="55" hidden="1" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>94</v>
+      <c r="E55" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>12</v>
@@ -2912,25 +2896,25 @@
     </row>
     <row r="56" hidden="1" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>94</v>
+      <c r="E56" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>12</v>
@@ -2938,25 +2922,25 @@
     </row>
     <row r="57" hidden="1" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>94</v>
+        <v>1</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>12</v>
@@ -2964,25 +2948,25 @@
     </row>
     <row r="58" hidden="1" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>90</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>12</v>
@@ -2990,25 +2974,25 @@
     </row>
     <row r="59" hidden="1" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
-      </c>
-      <c r="E59" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>92</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>12</v>
@@ -3016,25 +3000,25 @@
     </row>
     <row r="60" hidden="1" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>94</v>
+      <c r="E60" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>12</v>
@@ -3042,25 +3026,25 @@
     </row>
     <row r="61" hidden="1" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>94</v>
+        <v>2</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>12</v>
@@ -3068,25 +3052,25 @@
     </row>
     <row r="62" hidden="1" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
-      </c>
-      <c r="E62" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>92</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>12</v>
@@ -3094,51 +3078,48 @@
     </row>
     <row r="63" hidden="1" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
         <v>110</v>
-      </c>
-      <c r="D63" s="1">
-        <v>3</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" hidden="1" spans="1:8">
-      <c r="A64" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D64" s="1">
-        <v>3</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>76</v>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F64" t="s">
+        <v>110</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>12</v>
@@ -3146,22 +3127,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="F65" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="G65" t="s">
+        <v>110</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>12</v>
@@ -3169,25 +3153,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F66" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>12</v>
@@ -3195,25 +3179,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F67" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>12</v>
@@ -3221,25 +3205,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F68" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G68" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>12</v>
@@ -3247,25 +3231,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F69" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" t="s">
         <v>130</v>
-      </c>
-      <c r="G69" t="s">
-        <v>122</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>12</v>
@@ -3273,73 +3257,32 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F70" t="s">
+        <v>135</v>
+      </c>
+      <c r="G70" t="s">
         <v>133</v>
       </c>
-      <c r="G70" t="s">
-        <v>131</v>
-      </c>
       <c r="H70" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" t="s">
-        <v>8</v>
-      </c>
-      <c r="B71" t="s">
-        <v>134</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D71">
-        <v>4</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F71" t="s">
-        <v>136</v>
-      </c>
-      <c r="G71" t="s">
-        <v>134</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A74" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A70" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="equal" val="eng"/>
